--- a/ExcelTable/ConfigTable.xlsx
+++ b/ExcelTable/ConfigTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Abyssrium\AppinToss\ExcelTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\TileSystem\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF011B65-913C-4439-8096-1AE53E63FE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3096EB5-2BD9-4A45-8C4F-10EFC70C11B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="765" yWindow="855" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfigTable" sheetId="18" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,307 +55,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WorldShipRewardCooltime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShowDevilSayTextCoolTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다시뜨는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OfflineRewardMaxTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OfflineRewardRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FreeGachaCooltime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>StoneTalkMax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FishTalkMax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">int </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OfflineRewardMinTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartHeart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StoneLevelMax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxFishCreate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FishTankSetDefaultCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StoneGrowUp_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산호석 첫번째 외형 성장 레벨 (산호 늘어남)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StoneGrowUp_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산호석 두번째 외형 성장 레벨 (산호석 커짐 1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StoneGrowUp_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산호석 세번째 외형 성장 레벨 (산호석 커짐 2)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>월드맵</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>쿨타임</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오프라인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최소시간</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>오프라인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>최대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>오프라인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>보상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>배율</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -476,7 +180,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -505,11 +209,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
@@ -524,18 +223,12 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -549,12 +242,12 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -563,10 +256,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Excel Built-in Normal" xfId="4" xr:uid="{59CBF072-CDB2-4550-892F-A743BB9061F6}"/>
@@ -885,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="62.85546875" customWidth="1"/>
@@ -899,7 +588,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -922,216 +611,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5">
-        <v>3600</v>
+      <c r="C3" s="3">
+        <v>21600</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:4" ht="16.5">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="16.5">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>180</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1800</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="C4" s="3">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5">
-        <v>10</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3">
-        <v>21600</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3">
-        <v>20</v>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3">
-        <v>10</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3">
-        <v>45</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="3">
-        <v>10</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3">
-        <v>100</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3">
-        <v>200</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3">
-        <v>300</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3">
-        <v>7000</v>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3">
-        <v>99999</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="16.5">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3">
-        <v>10</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
